--- a/examples/example_output.xlsx
+++ b/examples/example_output.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Rejected" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Details" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Rejected" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E7D32"/>
+        <bgColor rgb="002E7D32"/>
       </patternFill>
     </fill>
     <fill>
@@ -63,12 +70,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -436,7 +446,621 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RANK</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>NAME</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>COLLEGE</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>GENDER</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>SCORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Priya Menon</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>W001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fergusson College</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Aarav Sharma</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Fergusson College</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tanvi Rao</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>W010</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>St. Xavier's</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kavya Nair</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>W006</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>St. Xavier's</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Divya Pillai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>W004</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Christ University</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ananya Bose</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>W003</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Loyola College</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Isha Kapoor</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>W009</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fergusson College</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Meera Joshi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>W005</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fergusson College</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sneha Iyer</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>W002</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>St. Xavier's</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rahul Verma</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M002</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>St. Xavier's</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Yash Gupta</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>M010</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>St. Xavier's</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Aditya Rao</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>M007</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Loyola College</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rohan Das</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>M006</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>St. Xavier's</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Vikram Singh</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>M004</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fergusson College</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nikhil Reddy</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>M009</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fergusson College</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pooja Desai</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>W008</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Christ University</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Karan Patel</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>M003</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Loyola College</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Arjun Nair</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>M005</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Christ University</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sameer Khan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>M008</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Christ University</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ritika Shah</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>W007</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Loyola College</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>840</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -451,47 +1075,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>RANK</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>NAME</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>COLLEGE</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>GENDER</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>EVENT NAME</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>PERFORMANCE TYPE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>RESULT</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>SCORE</t>
         </is>
@@ -503,17 +1127,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tanvi Rao</t>
+          <t>Priya Menon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>W010</t>
+          <t>W001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>St. Xavier's</t>
+          <t>Fergusson College</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,7 +1147,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1500m</t>
+          <t>200m</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -533,30 +1157,30 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4:15.60</t>
+          <t>24.10</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1083</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kavya Nair</t>
+          <t>Priya Menon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>W006</t>
+          <t>W001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>St. Xavier's</t>
+          <t>Fergusson College</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -566,40 +1190,40 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Long Jump</t>
+          <t>100m</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DISTANCE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1075</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Divya Pillai</t>
+          <t>Priya Menon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>W004</t>
+          <t>W001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Christ University</t>
+          <t>Fergusson College</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -609,78 +1233,78 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>800m</t>
+          <t>Long Jump</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>DISTANCE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2:05.31</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1069</v>
+        <v>988</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ananya Bose</t>
+          <t>Aarav Sharma</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>W003</t>
+          <t>M001</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Loyola College</t>
+          <t>Fergusson College</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>400m</t>
+          <t>Long Jump</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>DISTANCE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>54.20</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1043</v>
+        <v>943</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Isha Kapoor</t>
+          <t>Aarav Sharma</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>W009</t>
+          <t>M001</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -690,40 +1314,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>High Jump</t>
+          <t>200m</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DISTANCE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1043</v>
+        <v>939</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meera Joshi</t>
+          <t>Aarav Sharma</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>W005</t>
+          <t>M001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -733,12 +1357,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>100m Hurdles</t>
+          <t>100m</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -748,30 +1372,30 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1038</v>
+        <v>925</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Priya Menon</t>
+          <t>Tanvi Rao</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>W001</t>
+          <t>W010</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fergusson College</t>
+          <t>St. Xavier's</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -781,7 +1405,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>100m</t>
+          <t>1500m</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -791,25 +1415,25 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>4:15.60</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1011</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sneha Iyer</t>
+          <t>Kavya Nair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>W002</t>
+          <t>W006</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -824,50 +1448,50 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>200m</t>
+          <t>Long Jump</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>DISTANCE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>24.30</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1007</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rahul Verma</t>
+          <t>Divya Pillai</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>M002</t>
+          <t>W004</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>St. Xavier's</t>
+          <t>Christ University</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>200m</t>
+          <t>800m</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -877,83 +1501,83 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>2:05.31</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1004</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yash Gupta</t>
+          <t>Ananya Bose</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M010</t>
+          <t>W003</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>St. Xavier's</t>
+          <t>Loyola College</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>High Jump</t>
+          <t>400m</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DISTANCE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>54.20</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1002</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aditya Rao</t>
+          <t>Isha Kapoor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>M007</t>
+          <t>W009</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Loyola College</t>
+          <t>Fergusson College</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Long Jump</t>
+          <t>High Jump</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -963,40 +1587,40 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>997</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rohan Das</t>
+          <t>Meera Joshi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>M006</t>
+          <t>W005</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>St. Xavier's</t>
+          <t>Fergusson College</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>110m Hurdles</t>
+          <t>100m Hurdles</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1006,40 +1630,40 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>969</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vikram Singh</t>
+          <t>Sneha Iyer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M004</t>
+          <t>W002</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Fergusson College</t>
+          <t>St. Xavier's</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>800m</t>
+          <t>200m</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1049,30 +1673,30 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1:52.30</t>
+          <t>24.30</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>961</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nikhil Reddy</t>
+          <t>Rahul Verma</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M009</t>
+          <t>M002</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fergusson College</t>
+          <t>St. Xavier's</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1082,50 +1706,50 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Javelin Throw</t>
+          <t>200m</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DISTANCE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>68.40</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>936</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pooja Desai</t>
+          <t>Yash Gupta</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>W008</t>
+          <t>M010</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Christ University</t>
+          <t>St. Xavier's</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Javelin Throw</t>
+          <t>High Jump</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1135,30 +1759,30 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>52.35</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>936</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aarav Sharma</t>
+          <t>Aditya Rao</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>M007</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fergusson College</t>
+          <t>Loyola College</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1168,40 +1792,40 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>100m</t>
+          <t>Long Jump</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>DISTANCE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>925</v>
+        <v>997</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Karan Patel</t>
+          <t>Rohan Das</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>M003</t>
+          <t>M006</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Loyola College</t>
+          <t>St. Xavier's</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1211,7 +1835,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>400m</t>
+          <t>110m Hurdles</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1221,30 +1845,30 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>48.90</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>925</v>
+        <v>969</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Arjun Nair</t>
+          <t>Vikram Singh</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M005</t>
+          <t>M004</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Christ University</t>
+          <t>Fergusson College</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1254,7 +1878,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1500m</t>
+          <t>800m</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1264,30 +1888,30 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3:55.10</t>
+          <t>1:52.30</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>913</v>
+        <v>961</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sameer Khan</t>
+          <t>Nikhil Reddy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>M008</t>
+          <t>M009</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Christ University</t>
+          <t>Fergusson College</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1297,7 +1921,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shot Put</t>
+          <t>Javelin Throw</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1307,53 +1931,225 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>16.20</t>
+          <t>68.40</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>895</v>
+        <v>936</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pooja Desai</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>W008</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Christ University</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Javelin Throw</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DISTANCE</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>52.35</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Karan Patel</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>M003</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Loyola College</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>400m</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>48.90</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Arjun Nair</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>M005</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Christ University</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1500m</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3:55.10</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sameer Khan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>M008</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Christ University</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Shot Put</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DISTANCE</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Ritika Shah</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>W007</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Loyola College</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Shot Put</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>DISTANCE</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>14.10</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I25" t="n">
         <v>840</v>
       </c>
     </row>
@@ -1362,7 +2158,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1383,47 +2179,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ROW</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>NAME</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>COLLEGE</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>GENDER</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>EVENT NAME</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>PERFORMANCE TYPE</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>RESULT</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>REASON</t>
         </is>
@@ -1431,7 +2227,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1476,7 +2272,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>

--- a/examples/example_output.xlsx
+++ b/examples/example_output.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Details" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Rejected" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="College Ranking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Details" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Rejected" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +44,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006A1B9A"/>
+        <bgColor rgb="006A1B9A"/>
       </patternFill>
     </fill>
     <fill>
@@ -70,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -79,6 +86,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1060,6 +1070,112 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>RANK</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>COLLEGE</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>ATHLETES</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>SCORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fergusson College</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9810</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>St. Xavier's</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6140</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Christ University</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3813</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Loyola College</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3805</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1075,47 +1191,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>RANK</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>NAME</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>COLLEGE</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>GENDER</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>EVENT NAME</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>PERFORMANCE TYPE</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>RESULT</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>SCORE</t>
         </is>
@@ -2158,7 +2274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2179,47 +2295,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>ROW</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>NAME</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>COLLEGE</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>GENDER</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>EVENT NAME</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>PERFORMANCE TYPE</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>RESULT</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>REASON</t>
         </is>

--- a/examples/example_output.xlsx
+++ b/examples/example_output.xlsx
@@ -456,15 +456,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,25 +476,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>BIB NUMBER</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>NAME</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>COLLEGE</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>GENDER</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SCORE</t>
         </is>
@@ -505,25 +511,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Priya Menon</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>W001</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>3025</v>
       </c>
     </row>
@@ -533,25 +544,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Aarav Sharma</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>M001</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>2807</v>
       </c>
     </row>
@@ -561,25 +577,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Tanvi Rao</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>W010</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>St. Xavier's</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1083</v>
       </c>
     </row>
@@ -589,25 +610,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Kavya Nair</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>W006</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>St. Xavier's</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>1075</v>
       </c>
     </row>
@@ -617,25 +643,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Divya Pillai</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>W004</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Christ University</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>1069</v>
       </c>
     </row>
@@ -645,25 +676,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Ananya Bose</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>W003</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Loyola College</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>1043</v>
       </c>
     </row>
@@ -673,25 +709,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Isha Kapoor</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>W009</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>1043</v>
       </c>
     </row>
@@ -701,25 +742,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Meera Joshi</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>W005</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>1038</v>
       </c>
     </row>
@@ -729,25 +775,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Sneha Iyer</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>W002</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>St. Xavier's</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>1007</v>
       </c>
     </row>
@@ -757,25 +808,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Rahul Verma</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>M002</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>St. Xavier's</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>1004</v>
       </c>
     </row>
@@ -785,25 +841,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Yash Gupta</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>M010</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>St. Xavier's</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+          <t>110</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>1002</v>
       </c>
     </row>
@@ -813,25 +862,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>Aditya Rao</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>M007</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Loyola College</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>997</v>
       </c>
     </row>
@@ -841,25 +895,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Rohan Das</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>M006</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>St. Xavier's</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>969</v>
       </c>
     </row>
@@ -869,25 +928,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Vikram Singh</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>M004</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>961</v>
       </c>
     </row>
@@ -897,25 +961,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Nikhil Reddy</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>M009</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>936</v>
       </c>
     </row>
@@ -925,25 +994,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Pooja Desai</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>W008</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Christ University</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>936</v>
       </c>
     </row>
@@ -953,25 +1027,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Karan Patel</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>M003</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Loyola College</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>925</v>
       </c>
     </row>
@@ -981,25 +1060,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Arjun Nair</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>M005</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Christ University</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>913</v>
       </c>
     </row>
@@ -1009,25 +1089,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Sameer Khan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>M008</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Christ University</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>895</v>
       </c>
     </row>
@@ -1037,25 +1122,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Ritika Shah</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>W007</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Loyola College</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>840</v>
       </c>
     </row>
@@ -1127,10 +1217,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6140</v>
+        <v>5138</v>
       </c>
     </row>
     <row r="4">
@@ -1139,14 +1229,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Christ University</t>
+          <t>Loyola College</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3813</v>
+        <v>3805</v>
       </c>
     </row>
     <row r="5">
@@ -1155,14 +1245,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Loyola College</t>
+          <t>Christ University</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3805</v>
+        <v>2900</v>
       </c>
     </row>
   </sheetData>
@@ -1176,18 +1266,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1198,40 +1289,45 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
+          <t>BIB NUMBER</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
           <t>NAME</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>COLLEGE</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>GENDER</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>EVENT NAME</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>PERFORMANCE TYPE</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>RESULT</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>SCORE</t>
         </is>
@@ -1243,40 +1339,45 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Priya Menon</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>W001</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>200m</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>24.10</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1026</v>
       </c>
     </row>
@@ -1286,40 +1387,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Priya Menon</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>W001</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>100m</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>11.90</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1011</v>
       </c>
     </row>
@@ -1329,40 +1435,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Priya Menon</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>W001</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Long Jump</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>DISTANCE</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>5.95</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>988</v>
       </c>
     </row>
@@ -1372,40 +1483,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Aarav Sharma</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>M001</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Long Jump</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>DISTANCE</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>7.10</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>943</v>
       </c>
     </row>
@@ -1415,40 +1531,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Aarav Sharma</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>M001</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>200m</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>21.90</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>939</v>
       </c>
     </row>
@@ -1458,40 +1579,45 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Aarav Sharma</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>M001</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>100m</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>10.87</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>925</v>
       </c>
     </row>
@@ -1501,40 +1627,45 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Tanvi Rao</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>W010</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>St. Xavier's</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>1500m</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>4:15.60</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>1083</v>
       </c>
     </row>
@@ -1544,40 +1675,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Kavya Nair</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>W006</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>St. Xavier's</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Long Jump</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>DISTANCE</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>6.35</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1075</v>
       </c>
     </row>
@@ -1587,40 +1723,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Divya Pillai</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>W004</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Christ University</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>800m</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>2:05.31</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>1069</v>
       </c>
     </row>
@@ -1630,40 +1771,45 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Ananya Bose</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>W003</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Loyola College</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>400m</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>54.20</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>1043</v>
       </c>
     </row>
@@ -1673,40 +1819,45 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Isha Kapoor</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>W009</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>High Jump</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>DISTANCE</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>1.82</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>1043</v>
       </c>
     </row>
@@ -1716,40 +1867,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>Meera Joshi</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>W005</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>100m Hurdles</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>13.85</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>1038</v>
       </c>
     </row>
@@ -1759,40 +1915,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Sneha Iyer</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>W002</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>St. Xavier's</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>200m</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>24.30</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>1007</v>
       </c>
     </row>
@@ -1802,40 +1963,45 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Rahul Verma</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>M002</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>St. Xavier's</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>200m</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>21.44</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>1004</v>
       </c>
     </row>
@@ -1845,40 +2011,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Yash Gupta</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>M010</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>St. Xavier's</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+          <t>110</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>High Jump</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>DISTANCE</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>1002</v>
       </c>
     </row>
@@ -1888,40 +2047,45 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Aditya Rao</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>M007</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Loyola College</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Long Jump</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>DISTANCE</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>7.35</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>997</v>
       </c>
     </row>
@@ -1931,40 +2095,45 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Rohan Das</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>M006</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>St. Xavier's</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>110m Hurdles</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>14.55</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>969</v>
       </c>
     </row>
@@ -1974,40 +2143,45 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Vikram Singh</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>M004</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>800m</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>1:52.30</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>961</v>
       </c>
     </row>
@@ -2017,40 +2191,45 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Nikhil Reddy</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>M009</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Fergusson College</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Javelin Throw</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>DISTANCE</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>68.40</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>936</v>
       </c>
     </row>
@@ -2060,40 +2239,45 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Pooja Desai</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>W008</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Christ University</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Javelin Throw</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>DISTANCE</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>52.35</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>936</v>
       </c>
     </row>
@@ -2103,40 +2287,45 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Karan Patel</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>M003</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Loyola College</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>400m</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>48.90</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>925</v>
       </c>
     </row>
@@ -2146,40 +2335,41 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Arjun Nair</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>M005</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Christ University</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>1500m</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>3:55.10</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>913</v>
       </c>
     </row>
@@ -2189,40 +2379,45 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Sameer Khan</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>M008</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Christ University</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Shot Put</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>DISTANCE</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>16.20</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>895</v>
       </c>
     </row>
@@ -2232,40 +2427,45 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Ritika Shah</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>W007</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Loyola College</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Shot Put</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>DISTANCE</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>14.10</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>840</v>
       </c>
     </row>
@@ -2280,18 +2480,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2302,40 +2500,30 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>NAME</t>
+          <t>BIB NUMBER</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>GENDER</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>COLLEGE</t>
+          <t>EVENT NAME</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>GENDER</t>
+          <t>PERFORMANCE TYPE</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>EVENT NAME</t>
+          <t>RESULT</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>PERFORMANCE TYPE</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>RESULT</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>REASON</t>
         </is>
@@ -2347,40 +2535,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bad Event</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>X001</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unknown College</t>
+          <t>Tug of War</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>DISTANCE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tug of War</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>DISTANCE</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
         <is>
           <t>Unknown EVENT NAME: 'Tug of War'</t>
         </is>
@@ -2392,42 +2570,63 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bad Result</t>
+          <t>902</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>X002</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unknown College</t>
+          <t>100m</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>not-a-time</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Invalid RESULT: 'not-a-time'</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>100m</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>not-a-time</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Invalid RESULT: 'not-a-time'</t>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10.50</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BIB NUMBER is empty</t>
         </is>
       </c>
     </row>
